--- a/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
+++ b/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:32:36+00:00</t>
+    <t>2026-02-10T16:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
+++ b/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T16:08:04+00:00</t>
+    <t>2026-02-11T10:01:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
+++ b/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T10:01:23+00:00</t>
+    <t>2026-02-11T13:27:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
+++ b/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T13:27:23+00:00</t>
+    <t>2026-02-16T09:05:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
+++ b/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:05:27+00:00</t>
+    <t>2026-02-23T08:45:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
+++ b/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:45:40+00:00</t>
+    <t>2026-02-23T08:50:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
+++ b/420-contenu-fhir---mise-à-jour-de-lévaluation/ig/StructureDefinition-tddui-consent-accord.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T08:50:29+00:00</t>
+    <t>2026-02-23T15:48:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
